--- a/astro-site/public/dl/plan-negocio-polleria/plan-financiero-polleria.xlsx
+++ b/astro-site/public/dl/plan-negocio-polleria/plan-financiero-polleria.xlsx
@@ -873,7 +873,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materia prima de la comida sobre sus ventas: el pollo entero sale a un 38,8 % (el pollo es caro y se vende barato), el medio a un 35,8 %, las patatas a un 28 %, la ensaladilla a un 25 %, el menú de sala a un 24 % y las croquetas, hechas con el pollo del día anterior, a un 22 %: el pedido tipo para llevar queda en un 33 % y la sala en un 25 %. Un 31 % de media, más 1,5 puntos de merma (pollos que sobran y no llegan a croqueta, patata frita que se tira) y menos medio de redondeo. Cada 10 % que suba el pollo resta unos 6.700 € al resultado: el pollo es un precio estimado por el kit, pon el de tu proveedor y escandalla con la calculadora del pack</t>
+          <t>Materia prima de la comida sobre sus ventas: el pollo entero sale a un 38,8 % (el pollo es caro y se vende barato), el medio a un 35,8 %, las patatas a un 28 %, la ensaladilla a un 25 %, el menú de sala a un 26 % y las croquetas, hechas con el pollo del día anterior, a un 22 %: el pedido tipo para llevar queda en un 33 % y la sala en un 25 %. Un 31 % de media, más 1,5 puntos de merma (pollos que sobran y no llegan a croqueta, patata frita que se tira) y menos medio de redondeo. Cada 10 % que suba el pollo resta unos 6.700 € al resultado: el pollo es un precio estimado por el kit, pon el de tu proveedor y escandalla con la calculadora del pack</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="D36" s="48" t="inlineStr">
         <is>
-          <t>Unos 208 pollos por asador y semana de media; en verano, un 15 % más en el interior y hasta un 35 % más en la costa. El caso vende unos 302</t>
+          <t>Unos 208 pollos por asador y semana de media; en verano, un 15 % más en el interior y hasta un 35 % más en la costa. El caso vende unos 301</t>
         </is>
       </c>
       <c r="E36" s="29" t="n"/>

--- a/astro-site/public/dl/plan-negocio-polleria/plan-financiero-polleria.xlsx
+++ b/astro-site/public/dl/plan-negocio-polleria/plan-financiero-polleria.xlsx
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
         <v>0.03235433226794972</v>
       </c>
       <c r="D27" s="29" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Conducto de extracción exclusivo hasta cubierta, Instalación eléctrica trifásica, cuadro y boletín y Fontanería, separador de grasas, climatización e instalación de gas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Conducto de extracción exclusivo hasta cubierta, "&amp;"Instalación eléctrica trifásica, cuadro y boletín y Fontanería, separador de grasas, climatización e instalación de gas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el "&amp;"porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Conducto de extracción exclusivo hasta cubierta, Instalación eléctrica trifásica, cuadro y boletín y Fontanería, separador de grasas, climatización e instalación de gas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E27" s="29" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="C32" s="29" t="n"/>
       <c r="D32" s="29" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E32" s="29" t="n"/>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="C37" s="29" t="n"/>
       <c r="D37" s="26" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos y lanzamiento, Stock inicial: pollo, patata, aceite, envases y bebida, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B30-B35-B36,"0")&amp;" € de los "&amp;TEXT(B30,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos y lanzamiento, Stock inicial: pollo, patata, aceite, envases y bebida, Fianza del alquiler, Alquiler de los "&amp;"meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B30-B35-B36,"0")&amp;" € de los "&amp;TEXT(B30,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos y lanzamiento, Stock inicial: pollo, patata, aceite, envases y bebida, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman 58576 € de los 142176 € de inversión.</v>
       </c>
       <c r="E37" s="29" t="n"/>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="29" t="n"/>

--- a/astro-site/public/dl/plan-negocio-polleria/plan-financiero-polleria.xlsx
+++ b/astro-site/public/dl/plan-negocio-polleria/plan-financiero-polleria.xlsx
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-polleria/plan-financiero-polleria.xlsx
+++ b/astro-site/public/dl/plan-negocio-polleria/plan-financiero-polleria.xlsx
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
         <v>0.03235433226794972</v>
       </c>
       <c r="D27" s="29" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Conducto de extracción exclusivo hasta cubierta, Instalación eléctrica trifásica, cuadro y boletín y Fontanería, separador de grasas, climatización e instalación de gas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Conducto de extracción exclusivo hasta cubierta, "&amp;"Instalación eléctrica trifásica, cuadro y boletín y Fontanería, separador de grasas, climatización e instalación de gas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el "&amp;"porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Conducto de extracción exclusivo hasta cubierta, Instalación eléctrica trifásica, cuadro y boletín y Fontanería, separador de grasas, climatización e instalación de gas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E27" s="29" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="C32" s="29" t="n"/>
       <c r="D32" s="29" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E32" s="29" t="n"/>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="C37" s="29" t="n"/>
       <c r="D37" s="26" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos y lanzamiento, Stock inicial: pollo, patata, aceite, envases y bebida, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B30-B35-B36,"0")&amp;" € de los "&amp;TEXT(B30,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos y lanzamiento, Stock inicial: pollo, patata, aceite, envases y bebida, Fianza del alquiler, Alquiler de los "&amp;"meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B30-B35-B36,"0")&amp;" € de los "&amp;TEXT(B30,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos y lanzamiento, Stock inicial: pollo, patata, aceite, envases y bebida, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman 58576 € de los 142176 € de inversión.</v>
       </c>
       <c r="E37" s="29" t="n"/>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="29" t="n"/>
